--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584485.8325258442</v>
+        <v>584486</v>
       </c>
       <c r="R2" t="n">
-        <v>6407838.999466883</v>
+        <v>6407839</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102829</v>
+        <v>102835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102835</v>
+        <v>102836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102836</v>
+        <v>102863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102863</v>
+        <v>102869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102869</v>
+        <v>102876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102876</v>
+        <v>102880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102880</v>
+        <v>102887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102890</v>
+        <v>102895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102895</v>
+        <v>102903</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102903</v>
+        <v>102913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2025 artfynd.xlsx
+++ b/artfynd/A 34166-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>75177549</v>
       </c>
       <c r="B2" t="n">
-        <v>102913</v>
+        <v>103402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
